--- a/data/export/2026-10-11-operations.xlsx
+++ b/data/export/2026-10-11-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,33 +1076,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2394,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2499,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2527,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2630,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2595,22 +2643,22 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>06:58</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2691,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2746,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2807,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2826,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2862,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2923,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2942,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2978,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3039,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3058,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3094,2823 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-operations.xlsx
+++ b/data/export/2026-10-11-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1922,7 +1970,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2075,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2042,7 +2090,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2195,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2162,7 +2210,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,13 +2436,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2512,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2509,7 +2561,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2521,28 +2573,28 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2575,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2594,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2619,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2691,12 +2747,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2710,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2735,46 +2791,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2807,12 +2867,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2826,7 +2886,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2851,46 +2911,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2923,12 +2987,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2942,7 +3006,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2967,46 +3031,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3039,12 +3107,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3058,7 +3126,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3083,46 +3151,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3155,12 +3227,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3174,7 +3246,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3199,46 +3271,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3271,12 +3347,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3290,7 +3366,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,18 +3391,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3339,60 +3419,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3406,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3416,33 +3500,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3455,60 +3543,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:58</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3522,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3532,33 +3624,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3571,60 +3667,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3638,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3648,17 +3748,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3668,13 +3768,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3697,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3735,12 +3839,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3754,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3790,7 +3894,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3907,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3813,7 +3917,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3823,40 +3927,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3870,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3880,33 +3988,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3919,22 +4031,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3967,12 +4079,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3986,7 +4098,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4022,7 +4134,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4035,22 +4147,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4083,12 +4195,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4102,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4138,7 +4250,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4263,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4161,7 +4273,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4199,12 +4311,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4218,7 +4330,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4254,7 +4366,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4267,22 +4379,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4315,12 +4427,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4334,7 +4446,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:58</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4370,7 +4482,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4383,22 +4495,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4436,7 +4548,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4450,7 +4562,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4486,7 +4598,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4611,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4509,7 +4621,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4547,12 +4659,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4566,7 +4678,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4602,77 +4714,73 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4686,7 +4794,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4696,107 +4804,99 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4810,7 +4910,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4820,65 +4920,61 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4911,12 +5007,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4930,7 +5026,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4966,77 +5062,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5050,7 +5142,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5060,17 +5152,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5080,45 +5172,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5151,12 +5239,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5170,7 +5258,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5206,35 +5294,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5267,12 +5355,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5286,7 +5374,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5322,35 +5410,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5383,12 +5471,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5402,7 +5490,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5438,35 +5526,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5499,12 +5587,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5518,7 +5606,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5543,50 +5631,46 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5619,12 +5703,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5638,7 +5722,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5674,35 +5758,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5735,12 +5819,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5754,7 +5838,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5790,35 +5874,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5851,12 +5935,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5870,47 +5954,2899 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="AD46" s="2" t="inlineStr">
-        <is>
-          <t>2/9</t>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-operations.xlsx
+++ b/data/export/2026-10-11-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:AD84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1883,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1960,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2003,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2123,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2156,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2180,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2315,7 +2327,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2392,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2431,7 +2443,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2512,7 +2524,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2551,7 +2563,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2632,7 +2644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2671,7 +2683,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2752,7 +2764,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2872,7 +2884,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2992,7 +3004,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3112,7 +3124,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3232,7 +3244,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3276,17 +3288,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3299,22 +3311,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3347,12 +3359,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3366,7 +3378,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3391,92 +3403,84 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3490,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3500,107 +3504,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,22 +3624,22 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3649,82 +3649,78 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3748,65 +3744,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3839,12 +3835,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3883,18 +3879,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3907,24 +3907,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3937,24 +3937,24 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -4031,60 +4031,64 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4098,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4108,33 +4112,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -4147,52 +4155,56 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4200,7 +4212,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4214,7 +4226,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4224,33 +4236,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -4263,60 +4279,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4330,7 +4350,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4340,33 +4360,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -4379,60 +4403,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:58</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4446,7 +4474,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4456,33 +4484,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4495,60 +4527,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4562,7 +4598,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4572,33 +4608,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -4611,60 +4651,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:14</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4678,7 +4722,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4688,33 +4732,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4775,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4737,7 +4785,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4775,12 +4823,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4794,7 +4842,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4819,7 +4867,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4830,7 +4878,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4843,22 +4891,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4891,12 +4939,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4910,7 +4958,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:58</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4946,7 +4994,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -4959,22 +5007,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5007,12 +5055,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5026,7 +5074,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5062,7 +5110,7 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5075,22 +5123,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5123,12 +5171,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5142,7 +5190,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5178,7 +5226,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5239,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5201,7 +5249,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5239,12 +5287,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5258,7 +5306,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5294,7 +5342,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5307,32 +5355,32 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq39，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5355,12 +5403,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5368,13 +5416,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5410,7 +5474,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5423,22 +5487,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5471,12 +5535,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5490,7 +5554,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5526,7 +5590,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5539,22 +5603,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5587,12 +5651,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5606,7 +5670,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5642,7 +5706,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5719,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5665,7 +5729,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5703,12 +5767,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5722,7 +5786,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5758,7 +5822,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5835,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5781,7 +5845,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5819,12 +5883,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5838,7 +5902,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5874,7 +5938,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5951,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5897,7 +5961,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5935,12 +5999,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5954,7 +6018,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5990,7 +6054,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6067,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6013,7 +6077,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6051,12 +6115,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6070,7 +6134,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6106,7 +6170,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6183,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6129,7 +6193,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6172,7 +6236,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6186,7 +6250,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6222,7 +6286,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6299,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6245,7 +6309,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6283,12 +6347,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6302,7 +6366,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6338,7 +6402,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6415,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6361,7 +6425,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6399,12 +6463,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6418,7 +6482,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6443,22 +6507,18 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6531,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6481,7 +6541,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6524,7 +6584,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6538,7 +6598,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,22 +6623,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6591,22 +6647,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6644,7 +6700,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6658,7 +6714,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6683,92 +6739,84 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6782,7 +6830,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6792,107 +6840,99 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6906,7 +6946,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6916,17 +6956,17 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6941,82 +6981,78 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7030,7 +7066,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7040,17 +7076,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7065,82 +7101,78 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7154,7 +7186,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7164,65 +7196,61 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7255,12 +7283,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7274,7 +7302,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7304,83 +7332,83 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7394,7 +7422,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7404,17 +7432,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7429,40 +7457,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7495,12 +7523,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7514,7 +7542,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7539,46 +7567,50 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7611,12 +7643,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7630,7 +7662,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7665,40 +7697,40 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7731,12 +7763,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7750,7 +7782,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7775,46 +7807,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7847,12 +7883,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7866,7 +7902,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7891,7 +7927,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7902,7 +7938,7 @@
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7951,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7925,7 +7961,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7935,40 +7971,44 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7982,7 +8022,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7992,37 +8032,37 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8075,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8045,7 +8085,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8055,40 +8095,44 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8102,7 +8146,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8112,17 +8156,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8137,12 +8181,12 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8155,60 +8199,64 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8222,7 +8270,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8232,33 +8280,37 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8276,47 +8328,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8324,7 +8380,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8338,7 +8394,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8348,17 +8404,17 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8378,7 +8434,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8447,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8401,7 +8457,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8411,40 +8467,44 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8458,7 +8518,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8468,33 +8528,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8571,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8517,7 +8581,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8527,32 +8591,36 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8560,7 +8628,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8574,7 +8642,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8584,17 +8652,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8604,13 +8672,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8623,22 +8695,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8671,12 +8743,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8690,7 +8762,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8715,7 +8787,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8726,7 +8798,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8739,52 +8811,56 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8792,7 +8868,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8806,47 +8882,1695 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="X79" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AD70" s="2" t="inlineStr">
-        <is>
-          <t>2/12</t>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-operations.xlsx
+++ b/data/export/2026-10-11-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD84"/>
+  <dimension ref="A1:AD96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2371,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2404,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2428,17 +2432,17 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2448,12 +2452,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2491,32 +2495,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2524,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2548,17 +2556,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2568,12 +2576,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2611,32 +2619,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2644,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2668,17 +2680,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2688,17 +2700,17 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2803,7 +2815,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2851,32 +2863,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2884,7 +2900,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2908,17 +2924,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2928,12 +2944,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3004,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3043,7 +3059,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3058,7 +3074,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3163,7 +3179,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3244,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3298,7 +3314,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3380,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3480,7 +3496,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3534,7 +3550,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3616,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3644,12 +3660,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
@@ -3720,7 +3736,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3764,12 +3780,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3787,22 +3803,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3835,12 +3851,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3854,7 +3870,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3889,82 +3905,78 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3978,7 +3990,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3988,107 +4000,103 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4102,7 +4110,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4112,22 +4120,22 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4137,82 +4145,78 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4226,7 +4230,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4236,22 +4240,22 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4261,12 +4265,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4283,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4289,7 +4293,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4309,24 +4313,24 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4336,7 +4340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4350,7 +4354,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4385,12 +4389,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4407,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4413,7 +4417,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4433,24 +4437,24 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4460,7 +4464,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4474,7 +4478,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4509,12 +4513,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4531,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4537,7 +4541,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4557,34 +4561,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4598,7 +4602,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4633,12 +4637,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4651,24 +4655,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4681,12 +4685,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -4708,7 +4712,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4722,7 +4726,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4757,12 +4761,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4779,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4785,7 +4789,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4795,40 +4799,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4842,7 +4850,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4852,17 +4860,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4872,13 +4880,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4903,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4901,7 +4913,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4911,40 +4923,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4958,7 +4974,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4968,33 +4984,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5027,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5017,7 +5037,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5027,40 +5047,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5074,7 +5098,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5084,33 +5108,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5123,60 +5151,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:14</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5190,7 +5222,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5200,33 +5232,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5239,60 +5275,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5306,7 +5346,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:58</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5316,33 +5356,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5399,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5365,7 +5409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5375,40 +5419,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq39，推进2站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5416,29 +5464,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>物理seq23（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5448,33 +5480,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5523,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5497,7 +5533,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5507,40 +5543,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5554,7 +5594,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5564,33 +5604,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5647,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5613,7 +5657,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5623,40 +5667,44 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5670,7 +5718,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5680,33 +5728,37 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5771,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5729,7 +5781,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5739,12 +5791,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5767,12 +5819,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5780,13 +5832,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5822,7 +5890,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5903,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5845,7 +5913,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5883,12 +5951,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5902,7 +5970,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5938,7 +6006,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5951,7 +6019,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5961,7 +6029,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5999,12 +6067,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6018,7 +6086,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6054,7 +6122,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6067,22 +6135,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6115,12 +6183,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6134,7 +6202,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6170,7 +6238,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6183,22 +6251,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6231,12 +6299,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6250,7 +6318,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6286,7 +6354,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6299,22 +6367,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6347,12 +6415,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6366,7 +6434,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6402,7 +6470,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6415,22 +6483,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6463,12 +6531,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6482,7 +6550,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6518,7 +6586,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6531,22 +6599,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6584,7 +6652,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6598,7 +6666,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6634,7 +6702,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6647,22 +6715,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6695,12 +6763,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6714,7 +6782,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6750,7 +6818,7 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6763,22 +6831,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6811,12 +6879,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6830,7 +6898,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6866,7 +6934,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6879,22 +6947,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6932,7 +7000,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6946,7 +7014,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6971,22 +7039,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6999,22 +7063,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7052,7 +7116,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7066,7 +7130,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7091,22 +7155,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7119,22 +7179,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7167,12 +7227,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7186,7 +7246,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7222,7 +7282,7 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7295,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7245,7 +7305,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7288,7 +7348,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7302,7 +7362,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7337,12 +7397,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7415,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7365,7 +7425,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7408,7 +7468,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7422,7 +7482,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7457,12 +7517,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7535,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7485,7 +7545,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7523,12 +7583,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7542,7 +7602,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7567,22 +7627,18 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7595,22 +7651,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7648,7 +7704,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7662,7 +7718,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7697,12 +7753,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7771,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7763,12 +7819,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7782,7 +7838,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7817,12 +7873,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -7835,22 +7891,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7883,12 +7939,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7902,7 +7958,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7932,83 +7988,83 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8022,7 +8078,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8032,107 +8088,103 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8146,7 +8198,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8156,17 +8208,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8181,82 +8233,78 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8270,7 +8318,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8280,17 +8328,17 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8305,82 +8353,78 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8394,7 +8438,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8404,107 +8448,99 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8518,7 +8554,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8528,17 +8564,17 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8553,82 +8589,78 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8642,7 +8674,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8652,17 +8684,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8677,40 +8709,40 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8743,12 +8775,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8762,7 +8794,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8792,83 +8824,83 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8882,7 +8914,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8892,37 +8924,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8967,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8945,7 +8977,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8955,40 +8987,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9002,7 +9038,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9012,33 +9048,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9091,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9061,7 +9101,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9071,40 +9111,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9118,7 +9162,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9128,33 +9172,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9215,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9177,7 +9225,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9187,40 +9235,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9234,7 +9286,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9244,22 +9296,22 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9269,12 +9321,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9339,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9297,7 +9349,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9307,40 +9359,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9354,7 +9410,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9364,17 +9420,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9389,12 +9445,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9407,60 +9463,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9474,7 +9534,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9484,33 +9544,37 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9523,60 +9587,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9590,7 +9658,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9600,17 +9668,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9643,7 +9711,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9653,7 +9721,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9663,40 +9731,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9710,7 +9782,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9720,33 +9792,37 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9835,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9769,7 +9845,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9779,32 +9855,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9812,7 +9892,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9826,7 +9906,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9836,37 +9916,37 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB78" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9879,22 +9959,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9927,12 +10007,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9946,7 +10026,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9971,7 +10051,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9995,60 +10075,64 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10062,7 +10146,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10072,17 +10156,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10097,12 +10181,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10115,22 +10199,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10163,12 +10247,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10182,7 +10266,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10207,18 +10291,22 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10231,22 +10319,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -10279,12 +10367,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10298,7 +10386,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10323,18 +10411,22 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10439,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10357,7 +10449,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10395,12 +10487,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10414,7 +10506,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10439,7 +10531,7 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
@@ -10463,7 +10555,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10473,7 +10565,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10511,12 +10603,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10530,47 +10622,1467 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
+      <c r="X92" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y84" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB84" s="2" t="inlineStr">
+      <c r="AB92" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="AD84" s="2" t="inlineStr">
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-operations.xlsx
+++ b/data/export/2026-10-11-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4924,17 +4924,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5792,17 +5792,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6288,17 +6288,17 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7156,17 +7156,17 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7776,17 +7776,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8892,17 +8892,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9016,17 +9016,17 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -9803,32 +9803,36 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9836,7 +9840,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9860,17 +9864,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9880,17 +9884,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9923,32 +9927,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9956,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9980,17 +9988,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10000,17 +10008,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -10043,32 +10051,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10076,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10100,17 +10112,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10120,12 +10132,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10163,32 +10175,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -10196,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10220,17 +10236,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10240,12 +10256,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10316,7 +10332,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10370,7 +10386,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10452,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10480,17 +10496,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10824,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10852,17 +10868,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11196,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11234,7 +11250,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11374,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11568,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11676,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11720,17 +11736,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11940,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12044,7 +12060,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12180,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12304,7 +12320,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12428,7 +12444,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12676,7 +12692,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12800,7 +12816,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12920,7 +12936,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12969,12 +12985,12 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13184,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13346,7 +13362,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13432,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13465,7 +13481,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
@@ -13594,7 +13610,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13924,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13962,7 +13978,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -14032,7 +14048,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14076,17 +14092,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14474,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -14528,7 +14544,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14582,7 +14598,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14916,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14944,17 +14960,17 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15040,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15148,7 +15164,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15396,7 +15412,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15520,7 +15536,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15644,7 +15660,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15892,7 +15908,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16016,7 +16032,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16264,7 +16280,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16442,7 +16458,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16776,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16814,7 +16830,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17528,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17760,7 +17776,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -18008,7 +18024,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18310,7 +18326,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18450,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18946,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -19252,7 +19268,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19296,17 +19312,17 @@
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -19376,7 +19392,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19425,12 +19441,12 @@
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -19500,7 +19516,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19549,7 +19565,7 @@
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
@@ -19624,7 +19640,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19748,7 +19764,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19872,7 +19888,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19996,7 +20012,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20120,7 +20136,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20164,17 +20180,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20260,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20298,7 +20314,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -20368,7 +20384,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20422,7 +20438,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -20492,7 +20508,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20790,7 +20806,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20996,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21530,7 +21546,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -21852,7 +21868,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21949,24 +21965,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21976,7 +21992,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22025,12 +22041,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -22096,7 +22112,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22193,24 +22209,24 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O176" s="2" t="inlineStr">
@@ -22220,7 +22236,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22269,7 +22285,7 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
@@ -22307,32 +22323,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -22340,7 +22360,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22364,17 +22384,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22384,17 +22404,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -22427,12 +22447,12 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22460,7 +22480,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22468,10 +22488,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R178" s="2" t="inlineStr"/>
-      <c r="S178" s="2" t="inlineStr"/>
-      <c r="T178" s="2" t="inlineStr"/>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V178" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22547,32 +22583,36 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22580,7 +22620,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22604,17 +22644,17 @@
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA179" s="2" t="inlineStr">
@@ -22624,17 +22664,17 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -22700,7 +22740,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22787,12 +22827,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq48，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -22820,7 +22860,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22828,10 +22868,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R181" s="2" t="inlineStr"/>
-      <c r="S181" s="2" t="inlineStr"/>
-      <c r="T181" s="2" t="inlineStr"/>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V181" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22874,7 +22930,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -22940,7 +22996,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23060,7 +23116,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23180,7 +23236,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23234,7 +23290,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -23300,7 +23356,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23420,7 +23476,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23540,7 +23596,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23660,7 +23716,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23838,7 +23894,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -23962,7 +24018,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -24086,7 +24142,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24390,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -24706,7 +24762,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -24772,7 +24828,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24821,12 +24877,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24952,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24945,7 +25001,7 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
@@ -25074,7 +25130,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -25198,7 +25254,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25268,7 +25324,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25312,17 +25368,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -25562,7 +25618,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -25686,7 +25742,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -25756,7 +25812,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25800,12 +25856,12 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
@@ -25996,7 +26052,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26040,17 +26096,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26116,7 +26172,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26160,7 +26216,7 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
@@ -26414,7 +26470,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26484,7 +26540,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26533,12 +26589,12 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -26658,7 +26714,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -26724,7 +26780,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26773,7 +26829,7 @@
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -27026,7 +27082,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27150,7 +27206,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27276,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27264,17 +27320,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27464,7 +27520,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27508,12 +27564,12 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
@@ -27588,7 +27644,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27632,7 +27688,7 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
@@ -27766,7 +27822,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -27832,7 +27888,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27876,17 +27932,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -27956,7 +28012,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28005,7 +28061,7 @@
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
@@ -28254,7 +28310,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28324,7 +28380,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28368,17 +28424,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -28502,7 +28558,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -28572,7 +28628,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28616,12 +28672,12 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -28750,7 +28806,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -28820,7 +28876,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28864,17 +28920,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28944,7 +29000,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28988,7 +29044,7 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
@@ -29188,7 +29244,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29232,17 +29288,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -29366,7 +29422,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -29490,7 +29546,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -29614,7 +29670,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -29808,7 +29864,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29852,7 +29908,7 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
@@ -29932,7 +29988,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29981,12 +30037,12 @@
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -30052,7 +30108,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30101,7 +30157,7 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30176,7 +30232,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30220,17 +30276,17 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -30478,7 +30534,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -30602,7 +30658,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -30672,7 +30728,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30716,17 +30772,17 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -30920,7 +30976,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -30964,12 +31020,12 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
@@ -31098,7 +31154,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -31168,7 +31224,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31217,12 +31273,12 @@
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -31416,7 +31472,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31460,7 +31516,7 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
@@ -31540,7 +31596,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31589,7 +31645,7 @@
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
@@ -31664,7 +31720,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31708,17 +31764,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31912,7 +31968,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -31956,17 +32012,17 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32146,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -32214,7 +32270,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -32338,7 +32394,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -32408,7 +32464,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32452,17 +32508,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -32586,7 +32642,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -32656,7 +32712,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32700,12 +32756,12 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
@@ -32830,7 +32886,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -33144,7 +33200,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33193,12 +33249,12 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33324,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33312,7 +33368,7 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
@@ -33392,7 +33448,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33436,17 +33492,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33516,7 +33572,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33565,7 +33621,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33640,7 +33696,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33684,17 +33740,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33938,7 +33994,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -34058,7 +34114,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34234,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -34244,7 +34300,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34288,17 +34344,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -34422,7 +34478,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -34488,7 +34544,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34532,12 +34588,12 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
@@ -34790,7 +34846,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -34953,24 +35009,24 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N280" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O280" s="2" t="inlineStr">
@@ -34980,7 +35036,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35029,12 +35085,12 @@
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -35067,32 +35123,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35100,7 +35160,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35124,17 +35184,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35144,7 +35204,7 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
@@ -35274,7 +35334,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35394,7 +35454,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -35437,12 +35497,12 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
@@ -35464,7 +35524,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35513,7 +35573,7 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35551,32 +35611,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -35584,7 +35648,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35608,17 +35672,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35628,17 +35692,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35671,32 +35735,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -35704,7 +35772,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35728,17 +35796,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35748,17 +35816,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35791,32 +35859,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35824,7 +35896,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35848,17 +35920,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35868,17 +35940,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35911,32 +35983,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35944,7 +36020,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35968,17 +36044,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -35988,12 +36064,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36064,7 +36140,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36108,17 +36184,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -36184,7 +36260,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36228,17 +36304,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-11-operations.xlsx
+++ b/data/export/2026-10-11-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10185,24 +10185,24 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10299,32 +10299,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10332,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10356,17 +10360,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10376,12 +10380,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10419,32 +10423,36 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10452,7 +10460,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10476,17 +10484,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10496,12 +10504,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10754,7 +10762,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10886,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11010,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11204,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11240,17 +11248,17 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11382,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11870,7 +11878,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12002,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12204,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12444,7 +12452,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12488,17 +12496,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12700,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12736,12 +12744,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
@@ -12816,7 +12824,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12990,7 +12998,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13246,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13618,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -13854,7 +13862,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13932,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13978,7 +13986,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14110,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -14474,7 +14482,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14552,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14588,17 +14596,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -15040,7 +15048,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15218,7 +15226,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15350,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -15536,7 +15544,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15660,7 +15668,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15704,17 +15712,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -15908,7 +15916,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15952,12 +15960,12 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
@@ -16032,7 +16040,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16334,7 +16342,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -16458,7 +16466,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16784,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16830,7 +16838,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -17210,7 +17218,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -17458,7 +17466,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18032,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18068,12 +18076,12 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
@@ -18326,7 +18334,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -18698,7 +18706,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18954,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -19446,7 +19454,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19702,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19772,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19808,17 +19816,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -20066,7 +20074,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20198,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -20260,7 +20268,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20304,17 +20312,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20392,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20438,7 +20446,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20516,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20686,7 +20694,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20934,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -20996,7 +21004,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21298,7 +21306,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21554,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -21868,7 +21876,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -22046,7 +22054,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -22550,7 +22558,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22682,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22802,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -22832,7 +22840,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq48，推进20站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -22860,7 +22868,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22930,7 +22938,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -23083,32 +23091,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -23116,7 +23128,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23140,17 +23152,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23160,17 +23172,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -23203,32 +23215,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -23236,7 +23252,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23260,17 +23276,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23280,17 +23296,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -23323,32 +23339,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -23356,7 +23376,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23380,17 +23400,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23400,12 +23420,12 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
@@ -23476,7 +23496,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23596,7 +23616,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23716,7 +23736,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -24266,7 +24286,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24534,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25518,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -25812,7 +25832,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25861,12 +25881,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -25986,7 +26006,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26072,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26096,17 +26116,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26246,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26978,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -27454,7 +27474,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -27520,7 +27540,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27569,12 +27589,12 @@
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -27698,7 +27718,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27888,7 +27908,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27932,17 +27952,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -28628,7 +28648,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28677,12 +28697,12 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28896,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28920,17 +28940,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29074,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29244,7 +29264,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29794,7 +29814,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -29918,7 +29938,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30232,7 +30252,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30906,7 +30926,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -30976,7 +30996,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31025,12 +31045,12 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -31402,7 +31422,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31526,7 +31546,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -31720,7 +31740,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31764,17 +31784,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31968,7 +31988,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32712,7 +32732,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32761,12 +32781,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -33010,7 +33030,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -33130,7 +33150,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33378,7 +33398,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33468,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33492,17 +33512,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33696,7 +33716,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -34544,7 +34564,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34593,12 +34613,12 @@
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -34722,7 +34742,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -34966,7 +34986,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -35214,7 +35234,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -35648,7 +35668,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35692,17 +35712,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35772,7 +35792,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35993,24 +36013,24 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>21:58</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O288" s="2" t="inlineStr">
@@ -36020,7 +36040,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36069,12 +36089,12 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -36107,32 +36127,36 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr"/>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N289" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O289" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -36140,7 +36164,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36164,17 +36188,17 @@
       </c>
       <c r="X289" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z289" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA289" s="2" t="inlineStr">
@@ -36184,17 +36208,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -36260,7 +36284,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
